--- a/PlanB_分路径/Document_43/2_report/43号文必填信息.xlsx
+++ b/PlanB_分路径/Document_43/2_report/43号文必填信息.xlsx
@@ -7,9 +7,9 @@
     <workbookView windowWidth="28260" windowHeight="12460"/>
   </bookViews>
   <sheets>
-    <sheet name="普测" sheetId="1" r:id="rId1"/>
-    <sheet name="1000kV精测" sheetId="2" r:id="rId2"/>
-    <sheet name="500kV精测" sheetId="3" r:id="rId3"/>
+    <sheet name="43号文模板" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="程序自动将排在第一个的当做模板" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="38">
   <si>
     <t>序号</t>
   </si>
@@ -811,7 +811,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -833,6 +832,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1361,298 +1361,298 @@
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
-    <col min="10" max="10" width="15.6923076923077" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6923076923077" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="53" customHeight="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" ht="53" customHeight="1" spans="1:10">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="4">
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3">
         <v>1263</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" ht="53" customHeight="1" spans="1:10">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="4">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3">
         <v>1263</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" ht="53" customHeight="1" spans="1:10">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="4">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="3">
         <v>1263</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" ht="53" customHeight="1" spans="1:10">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="4">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="3">
         <v>1248</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="53" customHeight="1" spans="1:10">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="4">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="3">
         <v>1248</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="53" customHeight="1" spans="1:10">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="4">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="3">
         <v>1248</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" ht="53" customHeight="1" spans="1:10">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="4">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3">
         <v>1224</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" ht="53" customHeight="1" spans="1:10">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="4">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="3">
         <v>1224</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" ht="53" customHeight="1" spans="1:10">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="4">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="3">
         <v>1224</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" ht="53" customHeight="1" spans="1:10">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="4" t="s">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1665,9 +1665,302 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" ht="88" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="53" spans="1:10">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3">
+        <v>1263</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="53" spans="1:10">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="3">
+        <v>1263</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="53" spans="1:10">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="3">
+        <v>1263</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="53" spans="1:10">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="3">
+        <v>1248</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="53" spans="1:10">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="3">
+        <v>1248</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" ht="53" spans="1:10">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="3">
+        <v>1248</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="53" spans="1:10">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3">
+        <v>1224</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" ht="53" spans="1:10">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="3">
+        <v>1224</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="53" spans="1:10">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="3">
+        <v>1224</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" ht="53" spans="1:10">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
